--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES I-X/FRACC II/LTAIPT_A63F02B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2022/4TO_TRIMESTRE/FRACCIONES I-X/FRACC II/LTAIPT_A63F02B.xlsx
@@ -8,13 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
+    <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="Hidden_15">Hidden_1!$A$1:$A$2</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
   <si>
     <t>48948</t>
   </si>
@@ -43,6 +47,9 @@
     <t>7</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -64,6 +71,15 @@
     <t>435675</t>
   </si>
   <si>
+    <t>571907</t>
+  </si>
+  <si>
+    <t>571908</t>
+  </si>
+  <si>
+    <t>571909</t>
+  </si>
+  <si>
     <t>435676</t>
   </si>
   <si>
@@ -91,6 +107,15 @@
     <t>Hipervínculo al organigrama completo</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; ¿El sujeto obligado tiene entre sus atribuciones dar atención a temas relacionados con violencia y/o igualdad de género? (catálogo)</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Denominación del área/s que, de conformidad con sus atribuciones, dan atención a temas relacionados con violencia y/o igualdad de género</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; En su caso, denominación del Comité o instancia que atiende temas de género, aun cuando no cuente con atribuciones expresas para ello</t>
+  </si>
+  <si>
     <t>Área(s) responsable(s) que genera(n), posee(n), publica(n) y actualizan la información</t>
   </si>
   <si>
@@ -103,28 +128,34 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>5715FA9F094D2FD2FFA191B3B6A309A2</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>01/10/2022</t>
-  </si>
-  <si>
-    <t>31/12/2022</t>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Subdirección de Planeación y Evaluación Institucional</t>
+  </si>
+  <si>
+    <t>70917FFA8071445E3DA647A4DC09CD1C</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/03/2023</t>
   </si>
   <si>
     <t>http://cobatlaxcala.edu.mx/COBAT/assets/archivos/pdf/2022/organigrama_2022.pdf</t>
   </si>
   <si>
-    <t>Subdirección de Planeación y Evaluación</t>
-  </si>
-  <si>
-    <t>11/01/2023</t>
-  </si>
-  <si>
-    <t>s/n</t>
+    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
+  </si>
+  <si>
+    <t>18/04/2023</t>
+  </si>
+  <si>
+    <t>Si</t>
   </si>
 </sst>
 </file>
@@ -517,26 +548,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="70.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -553,7 +585,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -568,7 +600,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -585,44 +617,62 @@
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
         <v>10</v>
       </c>
       <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="L4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -632,65 +682,86 @@
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+    </row>
+    <row r="7" spans="1:12" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A6:L6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -698,6 +769,31 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F200">
+      <formula1>Hidden_15</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>